--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a8%d7%a1%d7%93%d7%a1-%d7%91%d7%a0%d7%93-%d7%98%d7%99%d7%a0%d7%93%d7%a8-%d7%92%d7%99%d7%a8%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "טינדר גירל" של מרסדס בנד מציג באופן אירוני, מלודי ולעיתים גם משעשע – אך בו־זמנית כואב – דיוקן של בדידות אנושית בעידן הדיגיטלי. מאחורי ההומור והקלילות המוזיקלית מסתתרת ביקורת חברתית עדינה על הדרך שבה טכנולוגיה, אפליקציות ואלגוריתמים מחליפים קשרים</v>
+        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>פן חזות – בואי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9f-%d7%97%d7%96%d7%95%d7%aa-%d7%91%d7%95%d7%90%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-29</v>
+        <v>2026-01-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
+        <v>השיר "בואי" של פן חזות הוא דוגמה מובהקת לאיך פשטות יכולה להפוך לעוצמה. אין כאן יומרה פיוטית גבוהה או תחכום לשוני מורכב – ובדיוק בגלל זה השיר עובד. הוא נשמע כמו וידוי שקט, כמעט יומן אישי, שמוגש בלחישה רגשית יותר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>פן חזות – בואי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פן חזות – בואי</v>
+        <v>איילאו &amp; אופק אדנק – מעגל</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9f-%d7%97%d7%96%d7%95%d7%aa-%d7%91%d7%95%d7%90%d7%99/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c%d7%90%d7%95-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%a2%d7%92%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בואי" של פן חזות הוא דוגמה מובהקת לאיך פשטות יכולה להפוך לעוצמה. אין כאן יומרה פיוטית גבוהה או תחכום לשוני מורכב – ובדיוק בגלל זה השיר עובד. הוא נשמע כמו וידוי שקט, כמעט יומן אישי, שמוגש בלחישה רגשית יותר</v>
+        <v>השיר "מעגל" בביצוע אייאלו ואופק אדנק הוא הצהרת כוונות ברורה: שיר מסיבה דאנסהול־ראפ שנועד בראש ובראשונה להזיז גוף, לייצר אנרגיה קהילתית ולבנות רגע של חופש. הוא לא מתיימר להיות יצירה פיוטית עמוקה – והכנות הזו היא חלק מהחוזק שלו. המשפט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פן חזות – בואי</v>
+        <v>איילאו &amp; אופק אדנק – מעגל</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-01-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איילאו &amp; אופק אדנק – מעגל</v>
+        <v>The Urban Tales Italian Diner ‏‫</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c%d7%90%d7%95-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%a2%d7%92%d7%9c/</v>
+        <v>https://yosmusic.com/the-urban-tales-italian-diner/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-30</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מעגל" בביצוע אייאלו ואופק אדנק הוא הצהרת כוונות ברורה: שיר מסיבה דאנסהול־ראפ שנועד בראש ובראשונה להזיז גוף, לייצר אנרגיה קהילתית ולבנות רגע של חופש. הוא לא מתיימר להיות יצירה פיוטית עמוקה – והכנות הזו היא חלק מהחוזק שלו. המשפט</v>
+        <v>השיר Italian Diner של הלהקה הישראלית The Urban Tales הוא פצצת פאנק־רוק תעשייתי, שמערב אלימות מילולית, הומור שחור וגרוטסקה כדי לתאר חוויה יומיומית לכאורה – עבודת מלצרות – כסיוט קפקאי. מאחורי הזעם והכאוס מסתתרת אמירה ברורה על ניצול, הזנחה מערכתית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איילאו &amp; אופק אדנק – מעגל</v>
+        <v>The Urban Tales Italian Diner ‏‫</v>
       </c>
     </row>
   </sheetData>
